--- a/backend/shipping/data/success.xlsx
+++ b/backend/shipping/data/success.xlsx
@@ -23,13 +23,13 @@
     <t>Date</t>
   </si>
   <si>
-    <t>90001481754</t>
+    <t>90001483456</t>
   </si>
   <si>
-    <t>CR176752718888</t>
+    <t>CR176760825626</t>
   </si>
   <si>
-    <t>2026-01-04T14:09:05.659764834</t>
+    <t>2026-01-05T13:27:02.594868313</t>
   </si>
 </sst>
 </file>

--- a/backend/shipping/data/success.xlsx
+++ b/backend/shipping/data/success.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>AWB No</t>
   </si>
@@ -23,13 +23,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>90001499711</t>
+    <t>80149521642</t>
   </si>
   <si>
-    <t>CR176853758626</t>
+    <t>CR176996649133</t>
   </si>
   <si>
-    <t>2026-01-16T09:56:42.9510945</t>
+    <t>2026-02-01T23:23:50.4572223</t>
+  </si>
+  <si>
+    <t>80149521653</t>
+  </si>
+  <si>
+    <t>CR176996649137</t>
+  </si>
+  <si>
+    <t>2026-02-01T23:23:51.6315691</t>
   </si>
 </sst>
 </file>
@@ -74,7 +83,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -99,6 +108,17 @@
         <v>5</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/backend/shipping/data/success.xlsx
+++ b/backend/shipping/data/success.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>AWB No</t>
   </si>
@@ -23,22 +23,13 @@
     <t>Date</t>
   </si>
   <si>
-    <t>80149521642</t>
+    <t>76727573941</t>
   </si>
   <si>
-    <t>CR176996649133</t>
+    <t>CR940121</t>
   </si>
   <si>
-    <t>2026-02-01T23:23:50.4572223</t>
-  </si>
-  <si>
-    <t>80149521653</t>
-  </si>
-  <si>
-    <t>CR176996649137</t>
-  </si>
-  <si>
-    <t>2026-02-01T23:23:51.6315691</t>
+    <t>2026-02-03T21:34:16.9444966</t>
   </si>
 </sst>
 </file>
@@ -83,7 +74,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -108,17 +99,6 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="s" s="0">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="C3" t="s" s="0">
-        <v>8</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
